--- a/artfynd/A 8304-2024 artfynd.xlsx
+++ b/artfynd/A 8304-2024 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>74660659</v>
       </c>
       <c r="B2" t="n">
-        <v>102078</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104449</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>554609.0863894999</v>
+        <v>554609</v>
       </c>
       <c r="R2" t="n">
-        <v>6262826.273085804</v>
+        <v>6262826</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>1987-07-07</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1987-07-07</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">

--- a/artfynd/A 8304-2024 artfynd.xlsx
+++ b/artfynd/A 8304-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74660659</v>
       </c>
       <c r="B2" t="n">
-        <v>104449</v>
+        <v>104458</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 8304-2024 artfynd.xlsx
+++ b/artfynd/A 8304-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74660659</v>
       </c>
       <c r="B2" t="n">
-        <v>104458</v>
+        <v>104461</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 8304-2024 artfynd.xlsx
+++ b/artfynd/A 8304-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74660659</v>
       </c>
       <c r="B2" t="n">
-        <v>104461</v>
+        <v>104488</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 8304-2024 artfynd.xlsx
+++ b/artfynd/A 8304-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74660659</v>
       </c>
       <c r="B2" t="n">
-        <v>104488</v>
+        <v>104494</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 8304-2024 artfynd.xlsx
+++ b/artfynd/A 8304-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74660659</v>
       </c>
       <c r="B2" t="n">
-        <v>104494</v>
+        <v>104501</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 8304-2024 artfynd.xlsx
+++ b/artfynd/A 8304-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74660659</v>
       </c>
       <c r="B2" t="n">
-        <v>104501</v>
+        <v>104505</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 8304-2024 artfynd.xlsx
+++ b/artfynd/A 8304-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74660659</v>
       </c>
       <c r="B2" t="n">
-        <v>104505</v>
+        <v>104512</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 8304-2024 artfynd.xlsx
+++ b/artfynd/A 8304-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74660659</v>
       </c>
       <c r="B2" t="n">
-        <v>104515</v>
+        <v>104520</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 8304-2024 artfynd.xlsx
+++ b/artfynd/A 8304-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74660659</v>
       </c>
       <c r="B2" t="n">
-        <v>104520</v>
+        <v>104528</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 8304-2024 artfynd.xlsx
+++ b/artfynd/A 8304-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74660659</v>
       </c>
       <c r="B2" t="n">
-        <v>104528</v>
+        <v>104538</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 8304-2024 artfynd.xlsx
+++ b/artfynd/A 8304-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>74660659</v>
+        <v>66279340</v>
       </c>
       <c r="B2" t="n">
-        <v>104538</v>
+        <v>81025</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1084</v>
+        <v>738</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Korndådra</t>
+          <t>Almlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neslia paniculata</t>
+          <t>Gyalecta ulmi</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Desv.</t>
+          <t>(Sw.) Zahlbr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Åker, rutans NV ruta i kant med ruta C1, S landsvägen mot Karsjö 4g SV C2, Sm</t>
+          <t>Västergården, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>554609</v>
+        <v>554505</v>
       </c>
       <c r="R2" t="n">
-        <v>6262826</v>
+        <v>6262845</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,17 +742,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1987-07-07</t>
+          <t>2017-06-14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1987-07-07</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Smålands flora 2007: KOO: 4G2b 4300. SOM: Neslia paniculata. LEG: Bengt Lundgren. KOM: Det. ThK</t>
+          <t>2017-06-14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -762,27 +759,228 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Åkerkant</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Aron Edman</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Aron Edman</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>74660659</v>
+      </c>
+      <c r="B3" t="n">
+        <v>105030</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1084</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Korndådra</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Neslia paniculata</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Desv.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Åker, rutans NV ruta i kant med ruta C1, S landsvägen mot Karsjö 4g SV C2, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>554609</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6262826</v>
+      </c>
+      <c r="S3" t="n">
+        <v>50</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Torsås</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Torsås</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>1987-07-07</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>1987-07-07</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Smålands flora 2007: KOO: 4G2b 4300. SOM: Neslia paniculata. LEG: Bengt Lundgren. KOM: Det. ThK</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Åkerkant</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Margareta Edqvist</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Via Margareta Edqvist</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="AY3" t="inlineStr">
         <is>
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>66279341</v>
+      </c>
+      <c r="B4" t="n">
+        <v>83314</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6471</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gulvit blekspik</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Sclerophora pallida</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Pers.) Y.J.Jao &amp; Spooner</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Västergården, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>554505</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6262845</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Torsås</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Torsås</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2017-06-14</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2017-06-14</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Aron Edman</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Aron Edman</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
